--- a/marketing/posts/convite-sap-bdc-innovation-day-agosto-2026/post-dados.xlsx
+++ b/marketing/posts/convite-sap-bdc-innovation-day-agosto-2026/post-dados.xlsx
@@ -865,17 +865,17 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Autoridade — Melhor Parceiro SAP BDC América Latina 2026</t>
+          <t>Case SSA Alimentos — unificação de dados com SAP Datasphere</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Evento</t>
+          <t>Case de cliente</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Por que ouvir a Solveplan sobre isso</t>
+          <t>Como a SSA Alimentos parou de operar com dados fragmentados</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -895,32 +895,33 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>Existe um motivo concreto pra Solveplan estar à frente dessa conversa sobre SAP Business Data Cloud: fomos reconhecidos como Melhor Parceiro SAP Business Data Cloud da América Latina em 2026.
-Não é selo de parede. É resultado de estar dentro da implementação — como parceira Gold SAP, com mais de 200 soluções entregues e 90 clientes atendidos em dados, analytics, planejamento financeiro e consolidação.
-Dia 26/08, na SAP Brasil, levamos esse repertório pro auditório: não uma apresentação institucional, uma demonstração de como o BDC resolve, na prática, o problema de dados fragmentados em empresas que rodam SAP.
-Pra quem decide sobre dados, TI e finanças nesse tipo de empresa, vale a manhã.
+          <t>A SSA Alimentos rodava SAP, mas vivia o mesmo problema de boa parte das empresas que atendemos: dados operacionais e financeiros espalhados entre sistemas, sem uma camada única que desse visão confiável pra quem decide.
+Com o SAP Datasphere, a Solveplan estruturou essa camada — unificando dados de diferentes fontes numa base governada, tirando a liderança da posição de reconciliar planilha antes de discutir resultado.
+Esse é o mesmo problema que resolvemos, em escala maior, com o SAP Business Data Cloud: unificar SAP e non-SAP numa camada só, pronta pra analytics e IA em tempo real.
+Dia 26/08, na SAP Brasil, mostramos como aplicar essa lógica com o BDC — com case real, não promessa institucional.
+Pra CIOs, CFOs, Controllers e Heads de Dados de empresas SAP.
 Inscrição (vagas limitadas): https://solveplan.com/evento/sap-innovation-day-dados-ia-sap-bdc/
-#SAPBDC #SAPGoldPartner #DataFoundation</t>
+#SAPBDC #SAPDatasphere #CaseDeSucesso</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>Somos reconhecidos como Melhor Parceiro SAP Business Data Cloud da América Latina em 2026 — parceria Gold SAP, +200 soluções entregues. Dia 26/08 levamos esse repertório pro auditório da SAP Brasil. Inscrição: https://solveplan.com/evento/sap-innovation-day-dados-ia-sap-bdc/</t>
+          <t>Case real: com o SAP Datasphere, unificamos os dados operacionais e financeiros da SSA Alimentos numa camada única e governada. Dia 26/08 mostramos como aplicar essa lógica em escala com o SAP Business Data Cloud. Inscrição: https://solveplan.com/evento/sap-innovation-day-dados-ia-sap-bdc/</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>Melhor Parceiro SAP Business Data Cloud da América Latina em 2026 🏆
-Não é selo de parede — é repertório de mais de 200 implementações levado pro auditório da SAP Brasil, dia 26/08.
-Dados, analytics, planejamento financeiro e consolidação, na prática.
+          <t>Case real: como a SSA Alimentos saiu dos dados fragmentados 📊
+Com o SAP Datasphere, unificamos dados operacionais e financeiros numa camada única — a liderança parou de reconciliar planilha pra discutir resultado.
+Dia 26/08 mostramos como aplicar essa lógica em escala com o SAP Business Data Cloud.
 📍 SAP Brasil · 🗓️ 26/08
 Link na bio — vagas limitadas
-#SAPBDC #SAPGoldPartner</t>
+#SAPBDC #SAPDatasphere #CaseDeSucesso</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>Imagem estática</t>
+          <t>Imagem estática / Carrossel</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr"/>
